--- a/Data/Results Files Log.xlsx
+++ b/Data/Results Files Log.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Jack\OneDrive - SEI\Yolo_Website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Jack\OneDrive - SEI\Yolo_Website\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EF43A1-74A3-42EF-ADDC-A890C207B88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C671AE0F-B40C-412E-8004-038E7E68C3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2597F6E-531F-4750-96F4-BBEC03A736ED}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2597F6E-531F-4750-96F4-BBEC03A736ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
   <si>
     <t>Groundwater Storage.csv</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Rumsey Gage Allocation Thresholds.csv</t>
   </si>
   <si>
-    <t>historic avg</t>
-  </si>
-  <si>
     <t>WEAP favorite</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>constant values</t>
   </si>
   <si>
-    <t>will be real result</t>
-  </si>
-  <si>
     <t>Forecast Outputs</t>
   </si>
   <si>
@@ -213,6 +207,48 @@
   </si>
   <si>
     <t>deleted (not used)</t>
+  </si>
+  <si>
+    <t>Water Year Types</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>historical values are constant, user must update prev and current WY as necessary</t>
+  </si>
+  <si>
+    <t>calculated</t>
+  </si>
+  <si>
+    <t>postprocessed value using VBS script; need to automize calculation</t>
+  </si>
+  <si>
+    <t>postprocessed value using VBS script</t>
+  </si>
+  <si>
+    <t>WEAP favorite\Groundwater\Groundwater Storage</t>
+  </si>
+  <si>
+    <t>Observed RMW Avg DTW.csv</t>
+  </si>
+  <si>
+    <t>Historical RMW Avg DTW.csv</t>
+  </si>
+  <si>
+    <t>historical avg</t>
+  </si>
+  <si>
+    <t>user must update annually</t>
+  </si>
+  <si>
+    <t>Reservoir Release-Capay Dam.csv</t>
+  </si>
+  <si>
+    <t>Reservoir Release-Irrigation.csv</t>
+  </si>
+  <si>
+    <t>Reservoir Release-Spill.csv</t>
   </si>
 </sst>
 </file>
@@ -266,7 +302,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" customWidth="1"/>
@@ -610,13 +646,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -624,7 +660,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -632,7 +668,7 @@
         <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -640,7 +676,7 @@
         <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -648,7 +684,7 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -656,10 +692,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -667,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -678,10 +714,10 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -689,10 +725,10 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -700,10 +736,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -711,10 +747,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -722,10 +758,10 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -733,10 +769,10 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -744,10 +780,10 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -755,26 +791,32 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
-        <v>50</v>
+      <c r="B17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -782,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -793,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -804,304 +846,373 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>14</v>
       </c>
-      <c r="B47" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" t="s">
-        <v>54</v>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C47" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A67">
-    <sortCondition ref="A2:A67"/>
+  <autoFilter ref="A1:C53" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A73">
+    <sortCondition ref="A2:A73"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Results Files Log.xlsx
+++ b/Data/Results Files Log.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Jack\OneDrive - SEI\Yolo_Website\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Users\Jack\OneDrive - SEI\Yolo_Website\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C671AE0F-B40C-412E-8004-038E7E68C3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0B1667-0243-4217-B603-29CBCC90AD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B2597F6E-531F-4750-96F4-BBEC03A736ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B2597F6E-531F-4750-96F4-BBEC03A736ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="74">
   <si>
     <t>Groundwater Storage.csv</t>
   </si>
@@ -92,12 +92,6 @@
     <t>Solano Decree-Season Remaining.csv</t>
   </si>
   <si>
-    <t>Reservoir Spills-Clear Lake.csv</t>
-  </si>
-  <si>
-    <t>Reservoir Spills-Indian Valley.csv</t>
-  </si>
-  <si>
     <t>Precipitation-Clear Lake Monthly.csv</t>
   </si>
   <si>
@@ -167,12 +161,6 @@
     <t>Historical Groundwater Storage.csv</t>
   </si>
   <si>
-    <t>dummy-forecast-diversions.csv</t>
-  </si>
-  <si>
-    <t>dummy-historical-diversions.csv</t>
-  </si>
-  <si>
     <t>YCFC Farmgate Deliveries Mar-Sep.csv</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>dummy</t>
-  </si>
-  <si>
     <t>historical model results</t>
   </si>
   <si>
@@ -206,12 +191,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>deleted (not used)</t>
-  </si>
-  <si>
-    <t>Water Year Types</t>
-  </si>
-  <si>
     <t>mixed</t>
   </si>
   <si>
@@ -221,9 +200,6 @@
     <t>calculated</t>
   </si>
   <si>
-    <t>postprocessed value using VBS script; need to automize calculation</t>
-  </si>
-  <si>
     <t>postprocessed value using VBS script</t>
   </si>
   <si>
@@ -249,13 +225,49 @@
   </si>
   <si>
     <t>Reservoir Release-Spill.csv</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>ImpactedWells.geojson</t>
+  </si>
+  <si>
+    <t>Precipitation-Davis catch Monthly.csv</t>
+  </si>
+  <si>
+    <t>Water Year Types.csv</t>
+  </si>
+  <si>
+    <t>WTandDTW.geojson</t>
+  </si>
+  <si>
+    <t>postprocessed values using Avg RMW DTW.vbs script</t>
+  </si>
+  <si>
+    <t>postprocessed values using Impacted Wells.vbs script</t>
+  </si>
+  <si>
+    <t>postprocessed values using WT and DTW.vbs script</t>
+  </si>
+  <si>
+    <t>not currently used</t>
+  </si>
+  <si>
+    <t>does not need to be updated</t>
+  </si>
+  <si>
+    <t>user must update annualy when GSP model complete</t>
+  </si>
+  <si>
+    <t>updated automatically  with forecast model run</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,18 +285,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -299,9 +323,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -637,582 +663,608 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="53.7109375" customWidth="1"/>
+    <col min="2" max="3" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
       <c r="B3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
       <c r="B5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>67</v>
-      </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>40</v>
       </c>
-      <c r="B34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>2</v>
-      </c>
-      <c r="B44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" t="s">
-        <v>46</v>
-      </c>
       <c r="C52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C53" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A73">
-    <sortCondition ref="A2:A73"/>
+  <autoFilter ref="A1:C49" xr:uid="{9B3E5313-6531-476C-969E-E5EB0B39DD2B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A65">
+    <sortCondition ref="A2:A65"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
